--- a/data/transacciones_mayo.xlsx
+++ b/data/transacciones_mayo.xlsx
@@ -413,10 +413,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M12"/>
+  <dimension ref="B2:M13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1"/>
     <row r="2">
       <c r="C2" t="inlineStr">
         <is>
@@ -424,7 +423,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="C4" t="inlineStr">
         <is>
@@ -449,7 +447,6 @@
         </is>
       </c>
     </row>
-    <row r="6"/>
     <row r="7">
       <c r="C7" t="inlineStr">
         <is>
@@ -603,6 +600,34 @@
       <c r="G12" t="inlineStr">
         <is>
           <t>Premio rifa del mes de febrero</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="n">
+        <v>4</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>May 2026</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>ITF</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Gasto</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Impuesto a transacciones financieras (traspase de cuenta)</t>
         </is>
       </c>
     </row>
